--- a/public/qr_metadata.xlsx
+++ b/public/qr_metadata.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Ad ID</t>
   </si>
@@ -25,28 +25,13 @@
     <t>Location Name</t>
   </si>
   <si>
-    <t>QR URL</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>https://jayse-precorneal-andy.ngrok-free.dev/track/TEST-home-aa3f4c015af95f1cbf996fd68f6371a5017063e2142752f8c9aaf3a4a96642af</t>
-  </si>
-  <si>
-    <t>testHome</t>
-  </si>
-  <si>
-    <t>https://jayse-precorneal-andy.ngrok-free.dev/track/TEST-testHome-7a3029106597b31c2490165a69975f4415568e320da7afb12c58155de16f3304</t>
-  </si>
-  <si>
-    <t>HOME</t>
-  </si>
-  <si>
-    <t>https://jayse-precorneal-andy.ngrok-free.dev/track/TEST-HOME-414858d85157228b1895ba32f67d6aa7d2888cc2e1fdcd684c6eb4317576548a</t>
+    <t>Scan URL</t>
+  </si>
+  <si>
+    <t>Redirect URL</t>
+  </si>
+  <si>
+    <t>URL Type</t>
   </si>
 </sst>
 </file>
@@ -423,17 +408,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="5" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,56 +435,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
